--- a/BWI/bestwine_output/bestwine_El Salvador.xlsx
+++ b/BWI/bestwine_output/bestwine_El Salvador.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA35"/>
+  <dimension ref="A1:AA38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -4106,6 +4106,249 @@
         </is>
       </c>
     </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>Grupo Steiner</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr"/>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>168782</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>El Salvador</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>Santa Elena</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>El Salvador</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>Bulevar Orden De Malta</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr"/>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gruposteiner.com</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr"/>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr"/>
+      <c r="M36" s="2" t="inlineStr"/>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>servicioalcliente@gruposteiner.com</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr"/>
+      <c r="P36" s="2" t="inlineStr"/>
+      <c r="Q36" s="2" t="inlineStr"/>
+      <c r="R36" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/grupo-steiner/</t>
+        </is>
+      </c>
+      <c r="S36" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/SteinerDistribuidora</t>
+        </is>
+      </c>
+      <c r="T36" s="2" t="inlineStr"/>
+      <c r="U36" s="2" t="inlineStr"/>
+      <c r="V36" s="2" t="inlineStr"/>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
+          <t>Javier Steiner</t>
+        </is>
+      </c>
+      <c r="X36" s="2" t="inlineStr">
+        <is>
+          <t>Ceo</t>
+        </is>
+      </c>
+      <c r="Y36" s="2" t="inlineStr"/>
+      <c r="Z36" s="2" t="inlineStr"/>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/javier-steiner/</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>Grupo Steiner</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr"/>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>168782</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>El Salvador</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>Santa Elena</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>El Salvador</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>Bulevar Orden De Malta</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr"/>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gruposteiner.com</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr"/>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr"/>
+      <c r="M37" s="2" t="inlineStr"/>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>servicioalcliente@gruposteiner.com</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr"/>
+      <c r="P37" s="2" t="inlineStr"/>
+      <c r="Q37" s="2" t="inlineStr"/>
+      <c r="R37" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/grupo-steiner/</t>
+        </is>
+      </c>
+      <c r="S37" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/SteinerDistribuidora</t>
+        </is>
+      </c>
+      <c r="T37" s="2" t="inlineStr"/>
+      <c r="U37" s="2" t="inlineStr"/>
+      <c r="V37" s="2" t="inlineStr"/>
+      <c r="W37" s="2" t="inlineStr">
+        <is>
+          <t>Yelena Martinez</t>
+        </is>
+      </c>
+      <c r="X37" s="2" t="inlineStr">
+        <is>
+          <t>Trade Development Manager</t>
+        </is>
+      </c>
+      <c r="Y37" s="2" t="inlineStr"/>
+      <c r="Z37" s="2" t="inlineStr"/>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/yelena-martinez-9a9a41212/</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>Grupo Steiner</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr"/>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>168782</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>El Salvador</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>Santa Elena</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>El Salvador</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>Bulevar Orden De Malta</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr"/>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gruposteiner.com</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr"/>
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr"/>
+      <c r="M38" s="2" t="inlineStr"/>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>servicioalcliente@gruposteiner.com</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr"/>
+      <c r="P38" s="2" t="inlineStr"/>
+      <c r="Q38" s="2" t="inlineStr"/>
+      <c r="R38" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/grupo-steiner/</t>
+        </is>
+      </c>
+      <c r="S38" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/SteinerDistribuidora</t>
+        </is>
+      </c>
+      <c r="T38" s="2" t="inlineStr"/>
+      <c r="U38" s="2" t="inlineStr"/>
+      <c r="V38" s="2" t="inlineStr"/>
+      <c r="W38" s="2" t="inlineStr">
+        <is>
+          <t>Raúl Padilla</t>
+        </is>
+      </c>
+      <c r="X38" s="2" t="inlineStr">
+        <is>
+          <t>Trade Development Manager</t>
+        </is>
+      </c>
+      <c r="Y38" s="2" t="inlineStr"/>
+      <c r="Z38" s="2" t="inlineStr"/>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/ra%C3%BAl-padilla-4a130b107/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
